--- a/business_surveys/026_sports_league_fan_experience_survey--business_surveys.xlsx
+++ b/business_surveys/026_sports_league_fan_experience_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'2-1',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '2-1', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2-2',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2-2', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'2-3',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '2-3', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'3-1',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '3-1', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'3-2',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '3-2', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'3-3',_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '3-3', 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'3-4',_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '3-4', 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'5-1',_'label':_'less_than_1/4_of_games'}</t>
+          <t>less_than_1/4_of_games</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '5-1', 'label': 'Less than 1/4 of games'}</t>
+          <t>Less than 1/4 of games</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'5-2',_'label':_'1/4_to_1/2_of_games'}</t>
+          <t>1/4_to_1/2_of_games</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '5-2', 'label': '1/4 to 1/2 of games'}</t>
+          <t>1/4 to 1/2 of games</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'5-3',_'label':_'1/2_to_3/4_of_games'}</t>
+          <t>1/2_to_3/4_of_games</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '5-3', 'label': '1/2 to 3/4 of games'}</t>
+          <t>1/2 to 3/4 of games</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'5-4',_'label':_'all_games'}</t>
+          <t>all_games</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '5-4', 'label': 'All games'}</t>
+          <t>All games</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'6-1',_'label':_'team_a'}</t>
+          <t>team_a</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '6-1', 'label': 'Team A'}</t>
+          <t>Team A</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'6-2',_'label':_'team_b'}</t>
+          <t>team_b</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': '6-2', 'label': 'Team B'}</t>
+          <t>Team B</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'6-3',_'label':_'team_c'}</t>
+          <t>team_c</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': '6-3', 'label': 'Team C'}</t>
+          <t>Team C</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'6-4',_'label':_'team_d'}</t>
+          <t>team_d</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': '6-4', 'label': 'Team D'}</t>
+          <t>Team D</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_'8-1',_'label':_'very_engaged'}</t>
+          <t>very_engaged</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': '8-1', 'label': 'Very Engaged'}</t>
+          <t>Very Engaged</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_'8-2',_'label':_'somewhat_engaged'}</t>
+          <t>somewhat_engaged</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': '8-2', 'label': 'Somewhat Engaged'}</t>
+          <t>Somewhat Engaged</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_'8-3',_'label':_'not_very_engaged'}</t>
+          <t>not_very_engaged</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': '8-3', 'label': 'Not Very Engaged'}</t>
+          <t>Not Very Engaged</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_'10-1',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': '10-1', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_'10-2',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': '10-2', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_'10-3',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': '10-3', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_'13-1',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': '13-1', 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_'13-2',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': '13-2', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_'13-3',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': '13-3', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_'13-4',_'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': '13-4', 'label': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_'14-1',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': '14-1', 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_'14-2',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': '14-2', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_'3-3',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': '3-3', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_'14-4',_'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': '14-4', 'label': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_'15-1',_'label':_'very_easy'}</t>
+          <t>very_easy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': '15-1', 'label': 'Very Easy'}</t>
+          <t>Very Easy</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_'15-2',_'label':_'somewhat_easy'}</t>
+          <t>somewhat_easy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': '15-2', 'label': 'Somewhat Easy'}</t>
+          <t>Somewhat Easy</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_'15-3',_'label':_'somewhat_hard'}</t>
+          <t>somewhat_hard</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': '15-3', 'label': 'Somewhat Hard'}</t>
+          <t>Somewhat Hard</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_'15-4',_'label':_'very_hard'}</t>
+          <t>very_hard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': '15-4', 'label': 'Very Hard'}</t>
+          <t>Very Hard</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_'16-1',_'label':_'very_clean'}</t>
+          <t>very_clean</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': '16-1', 'label': 'Very Clean'}</t>
+          <t>Very Clean</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_'16-2',_'label':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': '16-2', 'label': 'Clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_'16-3',_'label':_'somewhat_clean'}</t>
+          <t>somewhat_clean</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': '16-3', 'label': 'Somewhat Clean'}</t>
+          <t>Somewhat Clean</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_'16-4',_'label':_'not_very_clean'}</t>
+          <t>not_very_clean</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': '16-4', 'label': 'Not Very Clean'}</t>
+          <t>Not Very Clean</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_'17-1',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': '17-1', 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_'17-2',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': '17-2', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_'17-3',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': '17-3', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_'17-4',_'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': '17-4', 'label': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_'18-1',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': '18-1', 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_'18-2',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': '18-2', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_'18-3',_'label':_'somewhat_good'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': '18-3', 'label': 'Somewhat Good'}</t>
+          <t>Somewhat Good</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_'18-4',_'label':_'not_very_good'}</t>
+          <t>not_very_good</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': '18-4', 'label': 'Not Very Good'}</t>
+          <t>Not Very Good</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_'19-1',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': '19-1', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_'19-2',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': '19-2', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_'19-3',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': '19-3', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_'20-1',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': '20-1', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_'20-2',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': '20-2', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_'20-3',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': '20-3', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_'21-1',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': '21-1', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_'21-2',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': '21-2', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_'21-3',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': '21-3', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_'22-1',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': '22-1', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_'22-2',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': '22-2', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_'22-3',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': '22-3', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_'23-1',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': '23-1', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_'23-2',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': '23-2', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_'23-3',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': '23-3', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_'24-1',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': '24-1', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_'24-2',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': '24-2', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2197,12 +2197,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_'24-3',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': '24-3', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
